--- a/hourly datasets/cap_gen_year19final.xlsx
+++ b/hourly datasets/cap_gen_year19final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1131786086946073</v>
+        <v>0.1100121883085255</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1218613636993578</v>
+        <v>0.1199636320219565</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.235039972393965</v>
+        <v>0.229975820330482</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1375932818981117</v>
+        <v>0.1354953875175673</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.2507718905927189</v>
+        <v>0.2455075758260928</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04878831074351646</v>
+        <v>0.04121906772485127</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +539,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1619669194381237</v>
+        <v>0.1512312560333768</v>
       </c>
     </row>
     <row r="6">
@@ -549,25 +549,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0343649643497862</v>
+        <v>0.02515480622637715</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002158421334054636</v>
+        <v>0.00138996260199238</v>
       </c>
       <c r="D6" t="n">
-        <v>5.202212969087995</v>
+        <v>4.480972369150796</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02335440618728778</v>
+        <v>0.02125182424735426</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03013220212614183</v>
+        <v>0.02242860811359814</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03859772657343079</v>
+        <v>0.02788100433915588</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1475435730443935</v>
+        <v>0.1351669945349026</v>
       </c>
     </row>
     <row r="7">
@@ -577,25 +577,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02359404533206398</v>
+        <v>0.01324756331326301</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002039481093661821</v>
+        <v>0.0008227270204454504</v>
       </c>
       <c r="D7" t="n">
-        <v>4.688935704704987</v>
+        <v>3.751232719307348</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005642390157575884</v>
+        <v>0.002733107770121576</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01959212637235279</v>
+        <v>0.01163324585205197</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02759596429177455</v>
+        <v>0.0148618807744738</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1367726540266712</v>
+        <v>0.1232597516217885</v>
       </c>
     </row>
     <row r="8">
@@ -605,25 +605,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01941021750111112</v>
+        <v>0.008307799418634562</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001461175360400451</v>
+        <v>0.0007018860208619588</v>
       </c>
       <c r="D8" t="n">
-        <v>1.748050355832855</v>
+        <v>0.6627226222031153</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003696734588197441</v>
+        <v>0.0007743388559761817</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01654507921841213</v>
+        <v>0.00693124783181859</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02227535578380962</v>
+        <v>0.009684351005450533</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1325888261957184</v>
+        <v>0.11831998772716</v>
       </c>
     </row>
     <row r="9">
@@ -633,25 +633,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0166185622620552</v>
+        <v>0.005241421660407688</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001610544705972097</v>
+        <v>0.0005762302320725861</v>
       </c>
       <c r="D9" t="n">
-        <v>1.564815158547401</v>
+        <v>0.4984711565562281</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006230055483430611</v>
+        <v>0.0008331350384191082</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01346043771353193</v>
+        <v>0.004111690144577982</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01977668681057825</v>
+        <v>0.006371153176237401</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1297971709566625</v>
+        <v>0.1152536099689332</v>
       </c>
     </row>
     <row r="10">
@@ -661,25 +661,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01714509198296621</v>
+        <v>0.005618925335554472</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001629357016901622</v>
+        <v>0.0006105211252284123</v>
       </c>
       <c r="D10" t="n">
-        <v>1.51464351573503</v>
+        <v>0.4074409536966552</v>
       </c>
       <c r="E10" t="n">
-        <v>0.006553274137775946</v>
+        <v>5.061423045831165e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01395018109562983</v>
+        <v>0.004421947417918289</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02034000287030291</v>
+        <v>0.006815903253190931</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1303237006775735</v>
+        <v>0.1156311136440799</v>
       </c>
     </row>
     <row r="11">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02984110674673522</v>
+        <v>0.02913801658872414</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -697,7 +697,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1430197154413425</v>
+        <v>0.1391502048972496</v>
       </c>
     </row>
     <row r="12">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05641442708176776</v>
+        <v>0.05501572074861228</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -715,7 +715,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.169593035776375</v>
+        <v>0.1650279090571378</v>
       </c>
     </row>
     <row r="13">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07580404521182262</v>
+        <v>0.07330969101700063</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -733,7 +733,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1889826539064299</v>
+        <v>0.1833218793255261</v>
       </c>
     </row>
     <row r="14">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08310892516889606</v>
+        <v>0.08080049608589876</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -751,7 +751,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1962875338635033</v>
+        <v>0.1908126843944242</v>
       </c>
     </row>
     <row r="15">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0903514308826778</v>
+        <v>0.08738895970359918</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -769,7 +769,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.203530039577285</v>
+        <v>0.1974011480121247</v>
       </c>
     </row>
     <row r="16">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09514804186755348</v>
+        <v>0.09230634143060977</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -787,7 +787,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.2083266505621607</v>
+        <v>0.2023185297391352</v>
       </c>
     </row>
     <row r="17">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.09795295822564463</v>
+        <v>0.09502450865776076</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -805,7 +805,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.2111315669202519</v>
+        <v>0.2050366969662862</v>
       </c>
     </row>
     <row r="18">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1131786086946073</v>
+        <v>-0.1100121883085255</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.100736314709637</v>
+        <v>0.09828601449410253</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -841,7 +841,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.2139149234042443</v>
+        <v>0.208298202802628</v>
       </c>
     </row>
     <row r="20">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1025697862965416</v>
+        <v>0.09982544044835533</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -859,7 +859,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.2157483949911489</v>
+        <v>0.2098376287568808</v>
       </c>
     </row>
     <row r="21">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1063911053297102</v>
+        <v>0.104155638079888</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -877,7 +877,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.2195697140243175</v>
+        <v>0.2141678263884135</v>
       </c>
     </row>
     <row r="22">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1124193032281466</v>
+        <v>0.1093847876072464</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -895,7 +895,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.2255979119227538</v>
+        <v>0.2193969759157719</v>
       </c>
     </row>
     <row r="23">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1128603529604227</v>
+        <v>0.111890376885865</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -913,7 +913,7 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.22603896165503</v>
+        <v>0.2219025651943905</v>
       </c>
     </row>
     <row r="24">
@@ -923,25 +923,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1200310554705017</v>
+        <v>0.1171708060351258</v>
       </c>
       <c r="C24" t="n">
-        <v>0.006643996483768277</v>
+        <v>0.006234069208928108</v>
       </c>
       <c r="D24" t="n">
-        <v>1566163970759.371</v>
+        <v>1561514114324.375</v>
       </c>
       <c r="E24" t="n">
-        <v>0.02919966064840934</v>
+        <v>0.02592300052598165</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1069690528182446</v>
+        <v>0.1049138971902226</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1330930581227591</v>
+        <v>0.1294277148800296</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2332096641651089</v>
+        <v>0.2271829943436513</v>
       </c>
     </row>
     <row r="25">
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1211818174852429</v>
+        <v>0.1192108385563991</v>
       </c>
       <c r="C25" t="n">
-        <v>0.006686943135642252</v>
+        <v>0.006295957732939221</v>
       </c>
       <c r="D25" t="n">
-        <v>1509254108728.727</v>
+        <v>1504358845193.304</v>
       </c>
       <c r="E25" t="n">
-        <v>0.03270129652224789</v>
+        <v>0.02943518691485835</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1080363451759315</v>
+        <v>0.1068334118407719</v>
       </c>
       <c r="G25" t="n">
-        <v>0.134327289794554</v>
+        <v>0.1315882652720265</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2343604261798502</v>
+        <v>0.2292230268649245</v>
       </c>
     </row>
     <row r="26">
@@ -979,25 +979,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1248624877034587</v>
+        <v>0.1228609760472239</v>
       </c>
       <c r="C26" t="n">
-        <v>0.006532891869858073</v>
+        <v>0.006174543383285369</v>
       </c>
       <c r="D26" t="n">
-        <v>-126401847077.5133</v>
+        <v>-124669046466.9977</v>
       </c>
       <c r="E26" t="n">
-        <v>0.03369208752984119</v>
+        <v>0.02993068255454002</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1120239103561863</v>
+        <v>0.1107243609935218</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1377010650507302</v>
+        <v>0.1349975911009257</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2380410963980659</v>
+        <v>0.2328731643557493</v>
       </c>
     </row>
     <row r="27">
@@ -1007,25 +1007,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1283076976407428</v>
+        <v>0.1273987770679919</v>
       </c>
       <c r="C27" t="n">
-        <v>0.006600492221340341</v>
+        <v>0.006318631077542492</v>
       </c>
       <c r="D27" t="n">
-        <v>29.99144521546262</v>
+        <v>30.2035905448033</v>
       </c>
       <c r="E27" t="n">
-        <v>0.04451991747656985</v>
+        <v>0.04102045344124113</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1153362128591081</v>
+        <v>0.114979588403731</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1412791824223772</v>
+        <v>0.1398179657322529</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2414863063353501</v>
+        <v>0.2374109653765173</v>
       </c>
     </row>
     <row r="28">
@@ -1035,25 +1035,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1321520855296657</v>
+        <v>0.1310629401497032</v>
       </c>
       <c r="C28" t="n">
-        <v>0.006628135629196968</v>
+        <v>0.006143138039070608</v>
       </c>
       <c r="D28" t="n">
-        <v>2031777523345.456</v>
+        <v>2029669207887.337</v>
       </c>
       <c r="E28" t="n">
-        <v>0.07209140588759202</v>
+        <v>0.06769037617792932</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1191340085878469</v>
+        <v>0.1189969395733602</v>
       </c>
       <c r="G28" t="n">
-        <v>0.145170162471484</v>
+        <v>0.1431289407260453</v>
       </c>
       <c r="H28" t="n">
-        <v>0.245330694224273</v>
+        <v>0.2410751284582286</v>
       </c>
     </row>
     <row r="29">
@@ -1063,25 +1063,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0206156902622914</v>
+        <v>0.00801982250993122</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001483712743870398</v>
+        <v>0.00050890783611161</v>
       </c>
       <c r="D29" t="n">
-        <v>2.424025198025625</v>
+        <v>1.052197570674941</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01290611937003616</v>
+        <v>0.009351259926293551</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01770573049253632</v>
+        <v>0.007021931448344172</v>
       </c>
       <c r="G29" t="n">
-        <v>0.02352565003204622</v>
+        <v>0.009017713571518385</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1337942989568986</v>
+        <v>0.1180320108184567</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year19final.xlsx
+++ b/hourly datasets/cap_gen_year19final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2293389438143335</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1100121883085255</v>
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1093666769320715</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1199636320219565</v>
+        <v>0.4100830561652823</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.229975820330482</v>
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2901107892830204</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1354953875175673</v>
+        <v>0.4322673022248341</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.2455075758260928</v>
+        <v>4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3122950353425721</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +545,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04121906772485127</v>
+        <v>0.4134344018146549</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +553,10 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1512312560333768</v>
+        <v>22</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2934621349323928</v>
       </c>
     </row>
     <row r="6">
@@ -549,25 +566,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02515480622637715</v>
+        <v>0.3846611102135777</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00138996260199238</v>
+        <v>0.00347025624636163</v>
       </c>
       <c r="D6" t="n">
-        <v>4.480972369150796</v>
+        <v>7.492295968333701</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02125182424735426</v>
+        <v>0.2916340562937894</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02242860811359814</v>
+        <v>0.03281121475275108</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02788100433915588</v>
+        <v>0.04642091428870946</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1351669945349026</v>
+        <v>53</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2646888433313157</v>
       </c>
     </row>
     <row r="7">
@@ -577,25 +597,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01324756331326301</v>
+        <v>0.3649382929917614</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008227270204454504</v>
+        <v>0.003211386108872302</v>
       </c>
       <c r="D7" t="n">
-        <v>3.751232719307348</v>
+        <v>0.8515564010827914</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002733107770121576</v>
+        <v>0.003511946138095468</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01163324585205197</v>
+        <v>0.004188755462947707</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0148618807744738</v>
+        <v>0.01678376435950684</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1232597516217885</v>
+        <v>53</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2449660261094994</v>
       </c>
     </row>
     <row r="8">
@@ -605,25 +628,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008307799418634562</v>
+        <v>0.3293395795141563</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0007018860208619588</v>
+        <v>0.003973739573884874</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6627226222031153</v>
+        <v>-11.22237350393453</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0007743388559761817</v>
+        <v>0.0008364188834554834</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00693124783181859</v>
+        <v>-0.03866331889383996</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009684351005450533</v>
+        <v>-0.02308075949575021</v>
       </c>
       <c r="H8" t="n">
-        <v>0.11831998772716</v>
+        <v>53</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.2093673126318943</v>
       </c>
     </row>
     <row r="9">
@@ -633,25 +659,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.005241421660407688</v>
+        <v>0.3224722292194654</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0005762302320725861</v>
+        <v>0.004441222317707561</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4984711565562281</v>
+        <v>-10.20467071440696</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0008331350384191082</v>
+        <v>0.000926899963569121</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004111690144577982</v>
+        <v>-0.04651281065811929</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006371153176237401</v>
+        <v>-0.02909813392142394</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1152536099689332</v>
+        <v>53</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.2024999623372034</v>
       </c>
     </row>
     <row r="10">
@@ -661,25 +690,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.005618925335554472</v>
+        <v>0.325235265446997</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0006105211252284123</v>
+        <v>0.004360169797519633</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4074409536966552</v>
+        <v>-9.969309877667463</v>
       </c>
       <c r="E10" t="n">
-        <v>5.061423045831165e-07</v>
+        <v>5.427610663392105e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>0.004421947417918289</v>
+        <v>-0.04297342343581535</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006815903253190931</v>
+        <v>-0.02587653289219774</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1156311136440799</v>
+        <v>53</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.205262998564735</v>
       </c>
     </row>
     <row r="11">
@@ -689,7 +721,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02913801658872414</v>
+        <v>0.2759126501329918</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -697,7 +729,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1391502048972496</v>
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1559403832507298</v>
       </c>
     </row>
     <row r="12">
@@ -707,7 +742,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05501572074861228</v>
+        <v>0.3046361177018324</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -715,7 +750,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1650279090571378</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1846638508195703</v>
       </c>
     </row>
     <row r="13">
@@ -725,7 +763,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07330969101700063</v>
+        <v>0.3230973943450353</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -733,7 +771,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1833218793255261</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2031251274627733</v>
       </c>
     </row>
     <row r="14">
@@ -743,7 +784,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08080049608589876</v>
+        <v>0.3327437466504448</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -751,7 +792,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1908126843944242</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.2127714797681828</v>
       </c>
     </row>
     <row r="15">
@@ -761,7 +805,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08738895970359918</v>
+        <v>0.3402990450605864</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -769,7 +813,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1974011480121247</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2203267781783244</v>
       </c>
     </row>
     <row r="16">
@@ -779,7 +826,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.09230634143060977</v>
+        <v>0.34675747240489</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -787,7 +834,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.2023185297391352</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.226785205522628</v>
       </c>
     </row>
     <row r="17">
@@ -797,7 +847,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.09502450865776076</v>
+        <v>0.3510253549798525</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -805,7 +855,10 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.2050366969662862</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2310530880975905</v>
       </c>
     </row>
     <row r="18">
@@ -815,7 +868,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1100121883085255</v>
+        <v>0.119972266882262</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
@@ -823,6 +876,9 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -833,7 +889,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.09828601449410253</v>
+        <v>0.3531505790652741</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -841,7 +897,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.208298202802628</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2331783121830121</v>
       </c>
     </row>
     <row r="20">
@@ -851,7 +910,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.09982544044835533</v>
+        <v>0.3542468707729272</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -859,7 +918,10 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.2098376287568808</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2342746038906652</v>
       </c>
     </row>
     <row r="21">
@@ -869,7 +931,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.104155638079888</v>
+        <v>0.3592134804610576</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -877,7 +939,10 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.2141678263884135</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2392412135787955</v>
       </c>
     </row>
     <row r="22">
@@ -887,7 +952,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1093847876072464</v>
+        <v>0.3645818002431135</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -895,7 +960,10 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.2193969759157719</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2446095333608515</v>
       </c>
     </row>
     <row r="23">
@@ -905,7 +973,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.111890376885865</v>
+        <v>0.3686684841890897</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -913,7 +981,10 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.2219025651943905</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2486962173068277</v>
       </c>
     </row>
     <row r="24">
@@ -923,25 +994,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1171708060351258</v>
+        <v>0.3752573026858007</v>
       </c>
       <c r="C24" t="n">
-        <v>0.006234069208928108</v>
+        <v>0.006227056985668087</v>
       </c>
       <c r="D24" t="n">
-        <v>1561514114324.375</v>
+        <v>1561225235552.385</v>
       </c>
       <c r="E24" t="n">
-        <v>0.02592300052598165</v>
+        <v>0.0259063788637183</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1049138971902226</v>
+        <v>0.104767554593255</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1294277148800296</v>
+        <v>0.1292538426313537</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2271829943436513</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2552850358035387</v>
       </c>
     </row>
     <row r="25">
@@ -951,25 +1025,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1192108385563991</v>
+        <v>0.3799481544834981</v>
       </c>
       <c r="C25" t="n">
-        <v>0.006295957732939221</v>
+        <v>0.0062836248647677</v>
       </c>
       <c r="D25" t="n">
-        <v>1504358845193.304</v>
+        <v>1504053149171.777</v>
       </c>
       <c r="E25" t="n">
-        <v>0.02943518691485835</v>
+        <v>0.02941164797096606</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1068334118407719</v>
+        <v>0.1065713149213526</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1315882652720265</v>
+        <v>0.1312777644725289</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2292230268649245</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2599758876012361</v>
       </c>
     </row>
     <row r="26">
@@ -979,25 +1056,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1228609760472239</v>
+        <v>0.3846590906081984</v>
       </c>
       <c r="C26" t="n">
-        <v>0.006174543383285369</v>
+        <v>0.006158516951140314</v>
       </c>
       <c r="D26" t="n">
-        <v>-124669046466.9977</v>
+        <v>-124657492902.8597</v>
       </c>
       <c r="E26" t="n">
-        <v>0.02993068255454002</v>
+        <v>0.02990254158630671</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1107243609935218</v>
+        <v>0.1103772289570792</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1349975911009257</v>
+        <v>0.1345875606013723</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2328731643557493</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2646868237259364</v>
       </c>
     </row>
     <row r="27">
@@ -1007,25 +1087,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1273987770679919</v>
+        <v>0.391171532742734</v>
       </c>
       <c r="C27" t="n">
-        <v>0.006318631077542492</v>
+        <v>0.006296868341480237</v>
       </c>
       <c r="D27" t="n">
-        <v>30.2035905448033</v>
+        <v>30.11649228227919</v>
       </c>
       <c r="E27" t="n">
-        <v>0.04102045344124113</v>
+        <v>0.04097215418576527</v>
       </c>
       <c r="F27" t="n">
-        <v>0.114979588403731</v>
+        <v>0.1145192738928778</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1398179657322529</v>
+        <v>0.1392722423142545</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2374109653765173</v>
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2711992658604719</v>
       </c>
     </row>
     <row r="28">
@@ -1035,25 +1118,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1310629401497032</v>
+        <v>0.3957536434778022</v>
       </c>
       <c r="C28" t="n">
-        <v>0.006143138039070608</v>
+        <v>0.006079350495933436</v>
       </c>
       <c r="D28" t="n">
-        <v>2029669207887.337</v>
+        <v>2029127374315.889</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06769037617792932</v>
+        <v>0.06750922872439628</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1189969395733602</v>
+        <v>0.1179687714152444</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1431289407260453</v>
+        <v>0.1418505285357784</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2410751284582286</v>
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2757813765955401</v>
       </c>
     </row>
     <row r="29">
@@ -1063,25 +1149,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.00801982250993122</v>
+        <v>0.3710019418124436</v>
       </c>
       <c r="C29" t="n">
-        <v>0.00050890783611161</v>
+        <v>0.002501904672287137</v>
       </c>
       <c r="D29" t="n">
-        <v>1.052197570674941</v>
+        <v>2.233700057641818</v>
       </c>
       <c r="E29" t="n">
-        <v>0.009351259926293551</v>
+        <v>0.2301287307146473</v>
       </c>
       <c r="F29" t="n">
-        <v>0.007021931448344172</v>
+        <v>0.007111005450134039</v>
       </c>
       <c r="G29" t="n">
-        <v>0.009017713571518385</v>
+        <v>0.01692164504375748</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1180320108184567</v>
+        <v>53</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2510296749301816</v>
       </c>
     </row>
   </sheetData>
